--- a/survey_templates/022_pre_festival_survey--survey_templates.xlsx
+++ b/survey_templates/022_pre_festival_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>before_a_meal</t>
+          <t>after_petting_an_animal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Before a meal</t>
+          <t>After petting an animal</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>after_petting_an_animal</t>
+          <t>after_touching_raw_meat/poultry</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>After petting an animal</t>
+          <t>After touching raw meat/poultry</t>
         </is>
       </c>
     </row>
@@ -1972,29 +1972,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>after_touching_raw_meat/poultry</t>
+          <t>before_a_nap</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>After touching raw meat/poultry</t>
+          <t>Before a nap</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>handwashing_frequency_choices</t>
+          <t>contactless_payment_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>before_a_nap</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Before a nap</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2006,29 +2006,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>contactless_payment_choices</t>
+          <t>social_distancing_frequency_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2057,29 +2057,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>social_distancing_frequency_choices</t>
+          <t>handwashing_frequency_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2108,29 +2108,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>handwashing_frequency_2_choices</t>
+          <t>vaccination_availability_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2159,29 +2159,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>vaccination_availability_choices</t>
+          <t>have_you_been_vaccinated_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2210,29 +2210,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>have_you_been_vaccinated_choices</t>
+          <t>mask_availability_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2244,12 +2244,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2261,29 +2261,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>mask_availability_choices</t>
+          <t>travel_history_1_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes_-_international_travel</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes - International travel</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>yes_-_international_travel</t>
+          <t>yes_-_domestic_travel</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Yes - International travel</t>
+          <t>Yes - Domestic travel</t>
         </is>
       </c>
     </row>
@@ -2312,29 +2312,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>yes_-_domestic_travel</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Yes - Domestic travel</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>travel_history_1_choices</t>
+          <t>travel_frequency_1_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -2346,12 +2346,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2363,29 +2363,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>travel_frequency_1_choices</t>
+          <t>mask_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2414,29 +2414,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mask_choices</t>
+          <t>handwashing_1_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2465,29 +2465,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>handwashing_1_choices</t>
+          <t>social_distancing_1_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -2499,12 +2499,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2516,29 +2516,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>social_distancing_1_choices</t>
+          <t>travel_history_2_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>yes_-_international_travel</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Yes - International travel</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>yes_-_international_travel</t>
+          <t>yes_-_domestic_travel</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Yes - International travel</t>
+          <t>Yes - Domestic travel</t>
         </is>
       </c>
     </row>
@@ -2567,27 +2567,10 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>yes_-_domestic_travel</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
-        <is>
-          <t>Yes - Domestic travel</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>travel_history_2_choices</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
         <is>
           <t>No</t>
         </is>
